--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -29,7 +29,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="INDUSTRY_MAP">Assumptions!$S$5:$AB$40</definedName>
+    <definedName name="INDUSTRY_MAP">Assumptions!$S$5:$AF$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'Conclusion'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -3547,12 +3547,16 @@
           <t>Existing Loan</t>
         </is>
       </c>
-      <c r="C27" s="88" t="inlineStr"/>
+      <c r="C27" s="88" t="inlineStr">
+        <is>
+          <t>Existing loan / liability details, where applicable</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="82">
       <c r="B28" s="88" t="inlineStr">
         <is>
-          <t>Debt-service coverage year by year</t>
+          <t>DSCR — Debt-service coverage year by year</t>
         </is>
       </c>
       <c r="C28" s="132" t="n"/>
@@ -9451,7 +9455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AF75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="81" min="1" max="1"/>
@@ -9613,6 +9617,26 @@
           <t>Sales Plan</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Seeds &amp; inputs holding</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Harvested stock holding</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="82">
       <c r="B6" s="88" t="inlineStr">
@@ -9672,6 +9696,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Prepaid subscriptions holding</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="82">
       <c r="B7" s="88" t="inlineStr">
@@ -9731,6 +9775,26 @@
           <t>Sales Plan</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventory (goods for resale) holding</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="82">
       <c r="B8" s="88" t="inlineStr">
@@ -9794,6 +9858,26 @@
           <t>Sales Plan</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Raw material holding</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Finished goods holding</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="82">
       <c r="B9" s="88" t="inlineStr">
@@ -9857,6 +9941,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>F&amp;B &amp; guest-supplies holding</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Guest / corporate receivables</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="82">
       <c r="B10" s="88" t="inlineStr">
@@ -9920,6 +10024,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spares &amp; consumables holding</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="82">
       <c r="B11" s="88" t="inlineStr">
@@ -9930,7 +10054,7 @@
       <c r="C11" s="123" t="n"/>
       <c r="H11" s="118" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>months</t>
         </is>
       </c>
       <c r="S11" s="81" t="inlineStr">
@@ -9981,6 +10105,26 @@
       <c r="AB11" s="198" t="inlineStr">
         <is>
           <t>Revenue Plan</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Medicines &amp; consumables holding</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
         </is>
       </c>
     </row>
@@ -10046,6 +10190,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Courseware &amp; supplies holding</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Fee receivables</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="82">
       <c r="B13" s="88" t="inlineStr">
@@ -10109,6 +10273,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inventory holding</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="82">
       <c r="B14" s="88" t="inlineStr">
@@ -10172,6 +10356,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Construction material holding</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="82">
       <c r="B15" s="115" t="inlineStr">
@@ -10227,6 +10431,26 @@
       <c r="AB15" s="198" t="inlineStr">
         <is>
           <t>Revenue Plan</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage stock holding</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
         </is>
       </c>
     </row>
@@ -10291,6 +10515,26 @@
           <t>Revenue Plan</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fuel &amp; spares holding</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="82">
       <c r="B17" s="88" t="inlineStr">
@@ -10371,6 +10615,26 @@
       <c r="AB17" s="198" t="inlineStr">
         <is>
           <t>Sales Plan</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Yarn &amp; fabric holding</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Finished goods holding</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
         </is>
       </c>
     </row>
@@ -10440,6 +10704,26 @@
           <t>Sales Plan</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Components &amp; raw-material holding</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Finished goods holding</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="82">
       <c r="B19" s="115" t="inlineStr">
@@ -10495,6 +10779,26 @@
       <c r="AB19" s="198" t="inlineStr">
         <is>
           <t>Revenue Plan</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inventory-in-transit holding</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Work-in-progress holding</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Receivables / debtors</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Creditors / payables</t>
         </is>
       </c>
     </row>
@@ -11023,10 +11327,9 @@
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="82">
-      <c r="B50" s="88" t="inlineStr">
-        <is>
-          <t>Raw material holding</t>
-        </is>
+      <c r="B50" s="88">
+        <f>IFERROR(VLOOKUP($J$5,INDUSTRY_MAP,11,FALSE()),"Raw material holding")</f>
+        <v/>
       </c>
       <c r="C50" s="123" t="n"/>
       <c r="H50" s="118" t="inlineStr">
@@ -11036,10 +11339,9 @@
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="82">
-      <c r="B51" s="88" t="inlineStr">
-        <is>
-          <t>Finished goods holding</t>
-        </is>
+      <c r="B51" s="88">
+        <f>IFERROR(VLOOKUP($J$5,INDUSTRY_MAP,12,FALSE()),"Finished goods holding")</f>
+        <v/>
       </c>
       <c r="C51" s="123" t="n"/>
       <c r="H51" s="118" t="inlineStr">
@@ -11049,10 +11351,9 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="82">
-      <c r="B52" s="88" t="inlineStr">
-        <is>
-          <t>Receivables / debtors</t>
-        </is>
+      <c r="B52" s="88">
+        <f>IFERROR(VLOOKUP($J$5,INDUSTRY_MAP,13,FALSE()),"Receivables / debtors")</f>
+        <v/>
       </c>
       <c r="C52" s="123" t="n"/>
       <c r="H52" s="118" t="inlineStr">
@@ -11062,10 +11363,9 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="82">
-      <c r="B53" s="88" t="inlineStr">
-        <is>
-          <t>Creditors / payables</t>
-        </is>
+      <c r="B53" s="88">
+        <f>IFERROR(VLOOKUP($J$5,INDUSTRY_MAP,14,FALSE()),"Creditors / payables")</f>
+        <v/>
       </c>
       <c r="C53" s="123" t="n"/>
       <c r="H53" s="118" t="inlineStr">
@@ -11515,7 +11815,7 @@
     </row>
     <row r="11" ht="22" customHeight="1" s="82">
       <c r="B11" s="99">
-        <f>Form_III_BalanceSheet!$C$15</f>
+        <f>Assumptions!C3</f>
         <v/>
       </c>
       <c r="C11" s="105" t="n"/>
@@ -11710,10 +12010,9 @@
         <f>Ratios!G10</f>
         <v/>
       </c>
-      <c r="F77" s="107" t="inlineStr">
-        <is>
-          <t>Installed Capacity (p.a.)</t>
-        </is>
+      <c r="F77" s="107">
+        <f>IFERROR(VLOOKUP(Assumptions!$J$5,INDUSTRY_MAP,2,FALSE()),"Installed Capacity")</f>
+        <v/>
       </c>
       <c r="G77" s="111">
         <f>Assumptions!C16</f>
@@ -11781,10 +12080,9 @@
       <c r="H80" s="106" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="107" t="inlineStr">
-        <is>
-          <t>Raw Material Holding</t>
-        </is>
+      <c r="B81" s="107">
+        <f>IFERROR(VLOOKUP(Assumptions!$J$5,INDUSTRY_MAP,11,FALSE()),"Raw Material Holding")</f>
+        <v/>
       </c>
       <c r="C81" s="112">
         <f>Assumptions!C50</f>
@@ -11802,10 +12100,9 @@
       <c r="H81" s="106" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="107" t="inlineStr">
-        <is>
-          <t>Finished Goods Holding</t>
-        </is>
+      <c r="B82" s="107">
+        <f>IFERROR(VLOOKUP(Assumptions!$J$5,INDUSTRY_MAP,12,FALSE()),"Finished Goods Holding")</f>
+        <v/>
       </c>
       <c r="C82" s="112">
         <f>Assumptions!C51</f>
@@ -11823,10 +12120,9 @@
       <c r="H82" s="106" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="107" t="inlineStr">
-        <is>
-          <t>Receivables</t>
-        </is>
+      <c r="B83" s="107">
+        <f>IFERROR(VLOOKUP(Assumptions!$J$5,INDUSTRY_MAP,13,FALSE()),"Receivables")</f>
+        <v/>
       </c>
       <c r="C83" s="112">
         <f>Assumptions!C52</f>
@@ -11834,10 +12130,9 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="107" t="inlineStr">
-        <is>
-          <t>Payables</t>
-        </is>
+      <c r="B84" s="107">
+        <f>IFERROR(VLOOKUP(Assumptions!$J$5,INDUSTRY_MAP,14,FALSE()),"Payables")</f>
+        <v/>
       </c>
       <c r="C84" s="112">
         <f>Assumptions!C53</f>
@@ -13613,51 +13908,51 @@
         </is>
       </c>
       <c r="B11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="C11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="D11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="E11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="F11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="G11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="H11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="I11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="J11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="K11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="L11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="M11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="N11" s="274">
@@ -13884,51 +14179,51 @@
         </is>
       </c>
       <c r="B12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="C12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="D12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="E12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="F12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="G12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="H12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="I12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="J12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="K12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="L12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="M12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="N12" s="274">
@@ -14155,51 +14450,51 @@
         </is>
       </c>
       <c r="B13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="C13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="D13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="E13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="F13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="G13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="H13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="I13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="J13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="K13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="L13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="M13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="N13" s="274">
@@ -14426,51 +14721,51 @@
         </is>
       </c>
       <c r="B14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="C14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="D14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="E14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="F14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="G14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="H14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="I14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="J14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="K14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="L14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="M14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
         <v/>
       </c>
       <c r="N14" s="274">

--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -38,7 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="\₹#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00\x"/>
@@ -48,6 +48,7 @@
     <numFmt numFmtId="170" formatCode="₹#,##0;[Red](₹#,##0)"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.0"/>
+    <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);-"/>
   </numFmts>
   <fonts count="78">
     <font>
@@ -1092,7 +1093,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="334">
+  <cellXfs count="337">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1971,6 +1972,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9617,22 +9621,22 @@
           <t>Sales Plan</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC5" s="81" t="inlineStr">
         <is>
           <t>Seeds &amp; inputs holding</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" s="81" t="inlineStr">
         <is>
           <t>Harvested stock holding</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE5" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AF5" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -9696,22 +9700,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC6" s="81" t="inlineStr">
         <is>
           <t>Prepaid subscriptions holding</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE6" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF6" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -9775,22 +9779,22 @@
           <t>Sales Plan</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC7" s="81" t="inlineStr">
         <is>
           <t>Inventory (goods for resale) holding</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD7" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE7" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF7" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -9858,22 +9862,22 @@
           <t>Sales Plan</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC8" s="81" t="inlineStr">
         <is>
           <t>Raw material holding</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD8" s="81" t="inlineStr">
         <is>
           <t>Finished goods holding</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE8" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF8" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -9941,22 +9945,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC9" s="81" t="inlineStr">
         <is>
           <t>F&amp;B &amp; guest-supplies holding</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD9" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE9" s="81" t="inlineStr">
         <is>
           <t>Guest / corporate receivables</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF9" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10024,22 +10028,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC10" s="81" t="inlineStr">
         <is>
           <t>Spares &amp; consumables holding</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD10" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE10" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AF10" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10107,22 +10111,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC11" s="81" t="inlineStr">
         <is>
           <t>Medicines &amp; consumables holding</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD11" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE11" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF11" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10190,22 +10194,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC12" s="81" t="inlineStr">
         <is>
           <t>Courseware &amp; supplies holding</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD12" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE12" s="81" t="inlineStr">
         <is>
           <t>Fee receivables</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF12" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10273,22 +10277,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC13" s="81" t="inlineStr">
         <is>
           <t>Inventory holding</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD13" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE13" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF13" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10356,22 +10360,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC14" s="81" t="inlineStr">
         <is>
           <t>Construction material holding</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD14" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE14" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF14" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10433,22 +10437,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC15" s="81" t="inlineStr">
         <is>
           <t>Food &amp; beverage stock holding</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD15" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE15" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF15" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10515,22 +10519,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC16" s="81" t="inlineStr">
         <is>
           <t>Fuel &amp; spares holding</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD16" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE16" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF16" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10617,22 +10621,22 @@
           <t>Sales Plan</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC17" s="81" t="inlineStr">
         <is>
           <t>Yarn &amp; fabric holding</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD17" s="81" t="inlineStr">
         <is>
           <t>Finished goods holding</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE17" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF17" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10704,22 +10708,22 @@
           <t>Sales Plan</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC18" s="81" t="inlineStr">
         <is>
           <t>Components &amp; raw-material holding</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD18" s="81" t="inlineStr">
         <is>
           <t>Finished goods holding</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE18" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF18" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10781,22 +10785,22 @@
           <t>Revenue Plan</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC19" s="81" t="inlineStr">
         <is>
           <t>Inventory-in-transit holding</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD19" s="81" t="inlineStr">
         <is>
           <t>Work-in-progress holding</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE19" s="81" t="inlineStr">
         <is>
           <t>Receivables / debtors</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AF19" s="81" t="inlineStr">
         <is>
           <t>Creditors / payables</t>
         </is>
@@ -10866,6 +10870,11 @@
       <c r="N20" s="124" t="inlineStr">
         <is>
           <t>M12</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Gestation (months, 0-11)</t>
         </is>
       </c>
       <c r="S20" s="81" t="inlineStr">
@@ -10937,6 +10946,9 @@
       <c r="L21" s="126" t="n"/>
       <c r="M21" s="126" t="n"/>
       <c r="N21" s="126" t="n"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
       <c r="S21" s="81" t="inlineStr">
         <is>
           <t>Mining &amp; Minerals</t>
@@ -11110,7 +11122,22 @@
           <t>Direct wages &amp; salaries / month (Year 1)</t>
         </is>
       </c>
-      <c r="C32" s="121" t="n"/>
+      <c r="C32" s="121">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+      <c r="D32" s="335" t="n"/>
+      <c r="E32" s="336" t="n"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>(headcount)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>(₹ / employee / month)</t>
+        </is>
+      </c>
       <c r="H32" s="118" t="inlineStr">
         <is>
           <t>₹/month</t>
@@ -11494,6 +11521,16 @@
           <t>Price (₹ / unit)</t>
         </is>
       </c>
+      <c r="E65" s="81" t="inlineStr">
+        <is>
+          <t>Price escalation (annual %)</t>
+        </is>
+      </c>
+      <c r="F65" s="81" t="inlineStr">
+        <is>
+          <t>Volume growth (annual %)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="81" t="inlineStr">
@@ -11507,6 +11544,8 @@
       <c r="D66" s="189" t="n">
         <v>0</v>
       </c>
+      <c r="E66" s="334" t="n"/>
+      <c r="F66" s="334" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="81" t="inlineStr">
@@ -11520,6 +11559,8 @@
       <c r="D67" s="189" t="n">
         <v>0</v>
       </c>
+      <c r="E67" s="334" t="n"/>
+      <c r="F67" s="334" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="81" t="inlineStr">
@@ -11533,6 +11574,8 @@
       <c r="D68" s="189" t="n">
         <v>0</v>
       </c>
+      <c r="E68" s="334" t="n"/>
+      <c r="F68" s="334" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="81" t="inlineStr">
@@ -11546,6 +11589,8 @@
       <c r="D69" s="189" t="n">
         <v>0</v>
       </c>
+      <c r="E69" s="334" t="n"/>
+      <c r="F69" s="334" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="257" t="inlineStr">
@@ -13908,51 +13953,51 @@
         </is>
       </c>
       <c r="B11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="C11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="D11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="E11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="F11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="G11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="H11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="I11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="J11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="K11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="L11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="M11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$66*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^0</f>
         <v/>
       </c>
       <c r="N11" s="274">
@@ -13960,51 +14005,51 @@
         <v/>
       </c>
       <c r="O11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="P11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="Q11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="R11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="S11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="T11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="U11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="V11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="W11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="X11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="Y11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="Z11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^1</f>
         <v/>
       </c>
       <c r="AA11" s="274">
@@ -14012,51 +14057,51 @@
         <v/>
       </c>
       <c r="AB11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AC11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AD11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AE11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AF11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AG11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AH11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AI11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AJ11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AK11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AL11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AM11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^2</f>
         <v/>
       </c>
       <c r="AN11" s="274">
@@ -14064,51 +14109,51 @@
         <v/>
       </c>
       <c r="AO11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AP11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AQ11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AR11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AS11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AT11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AU11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AV11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AW11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AX11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AY11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="AZ11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^3</f>
         <v/>
       </c>
       <c r="BA11" s="274">
@@ -14116,51 +14161,51 @@
         <v/>
       </c>
       <c r="BB11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BC11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BD11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BE11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BF11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BG11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BH11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BI11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BJ11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BK11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BL11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BM11" s="274">
-        <f>Assumptions!$C$66*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$66*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$66)^4</f>
         <v/>
       </c>
       <c r="BN11" s="274">
@@ -14179,51 +14224,51 @@
         </is>
       </c>
       <c r="B12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="C12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="D12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="E12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="F12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="G12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="H12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="I12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="J12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="K12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="L12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="M12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$67*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^0</f>
         <v/>
       </c>
       <c r="N12" s="274">
@@ -14231,51 +14276,51 @@
         <v/>
       </c>
       <c r="O12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="P12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="Q12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="R12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="S12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="T12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="U12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="V12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="W12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="X12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="Y12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="Z12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^1</f>
         <v/>
       </c>
       <c r="AA12" s="274">
@@ -14283,51 +14328,51 @@
         <v/>
       </c>
       <c r="AB12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AC12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AD12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AE12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AF12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AG12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AH12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AI12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AJ12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AK12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AL12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AM12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^2</f>
         <v/>
       </c>
       <c r="AN12" s="274">
@@ -14335,51 +14380,51 @@
         <v/>
       </c>
       <c r="AO12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AP12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AQ12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AR12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AS12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AT12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AU12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AV12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AW12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AX12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AY12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="AZ12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^3</f>
         <v/>
       </c>
       <c r="BA12" s="274">
@@ -14387,51 +14432,51 @@
         <v/>
       </c>
       <c r="BB12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BC12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BD12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BE12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BF12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BG12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BH12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BI12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BJ12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BK12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BL12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BM12" s="274">
-        <f>Assumptions!$C$67*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$67*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$67)^4</f>
         <v/>
       </c>
       <c r="BN12" s="274">
@@ -14450,51 +14495,51 @@
         </is>
       </c>
       <c r="B13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="C13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="D13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="E13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="F13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="G13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="H13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="I13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="J13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="K13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="L13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="M13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$68*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^0</f>
         <v/>
       </c>
       <c r="N13" s="274">
@@ -14502,51 +14547,51 @@
         <v/>
       </c>
       <c r="O13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="P13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="Q13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="R13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="S13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="T13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="U13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="V13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="W13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="X13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="Y13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="Z13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^1</f>
         <v/>
       </c>
       <c r="AA13" s="274">
@@ -14554,51 +14599,51 @@
         <v/>
       </c>
       <c r="AB13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AC13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AD13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AE13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AF13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AG13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AH13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AI13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AJ13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AK13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AL13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AM13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^2</f>
         <v/>
       </c>
       <c r="AN13" s="274">
@@ -14606,51 +14651,51 @@
         <v/>
       </c>
       <c r="AO13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AP13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AQ13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AR13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AS13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AT13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AU13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AV13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AW13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AX13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AY13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="AZ13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^3</f>
         <v/>
       </c>
       <c r="BA13" s="274">
@@ -14658,51 +14703,51 @@
         <v/>
       </c>
       <c r="BB13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BC13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BD13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BE13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BF13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BG13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BH13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BI13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BJ13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BK13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BL13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BM13" s="274">
-        <f>Assumptions!$C$68*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$68*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$68)^4</f>
         <v/>
       </c>
       <c r="BN13" s="274">
@@ -14721,51 +14766,51 @@
         </is>
       </c>
       <c r="B14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="C14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="D14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="E14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="F14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="G14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="H14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="I14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="J14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="K14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="L14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="M14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))</f>
+        <f>Assumptions!$C$69*Assumptions!$C$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^0</f>
         <v/>
       </c>
       <c r="N14" s="274">
@@ -14773,51 +14818,51 @@
         <v/>
       </c>
       <c r="O14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="P14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="Q14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="R14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="S14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="T14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="U14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="V14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="W14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="X14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="Y14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="Z14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$D$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$D$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^1</f>
         <v/>
       </c>
       <c r="AA14" s="274">
@@ -14825,51 +14870,51 @@
         <v/>
       </c>
       <c r="AB14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AC14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AD14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AE14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AF14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AG14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AH14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AI14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AJ14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AK14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AL14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AM14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$E$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$E$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^2</f>
         <v/>
       </c>
       <c r="AN14" s="274">
@@ -14877,51 +14922,51 @@
         <v/>
       </c>
       <c r="AO14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AP14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AQ14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AR14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AS14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AT14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AU14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AV14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AW14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AX14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AY14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="AZ14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$F$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$F$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^3</f>
         <v/>
       </c>
       <c r="BA14" s="274">
@@ -14929,51 +14974,51 @@
         <v/>
       </c>
       <c r="BB14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!C$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BC14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!D$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BD14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!E$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BE14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!F$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BF14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!G$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BG14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!H$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BH14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!I$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BI14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!J$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BJ14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!K$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BK14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!L$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BL14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!M$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BM14" s="274">
-        <f>Assumptions!$C$69*Assumptions!$G$18/12</f>
+        <f>Assumptions!$C$69*Assumptions!$G$18/12*IF(SUM(Assumptions!$C$21:$N$21)=0,1,12*Assumptions!N$21/SUM(Assumptions!$C$21:$N$21))*(1+Assumptions!$F$69)^4</f>
         <v/>
       </c>
       <c r="BN14" s="274">
@@ -21657,51 +21702,51 @@
         </is>
       </c>
       <c r="B11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="C11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="D11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="E11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="F11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="G11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="H11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="I11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="J11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="K11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="L11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="M11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^0</f>
         <v/>
       </c>
       <c r="N11" s="290">
@@ -21709,51 +21754,51 @@
         <v/>
       </c>
       <c r="O11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="P11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="Q11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="R11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="S11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="T11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="U11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="V11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="W11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="X11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="Y11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="Z11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^1</f>
         <v/>
       </c>
       <c r="AA11" s="290">
@@ -21761,51 +21806,51 @@
         <v/>
       </c>
       <c r="AB11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AC11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AD11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AE11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AF11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AG11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AH11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AI11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AJ11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AK11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AL11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AM11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^2</f>
         <v/>
       </c>
       <c r="AN11" s="290">
@@ -21813,51 +21858,51 @@
         <v/>
       </c>
       <c r="AO11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AP11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AQ11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AR11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AS11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AT11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AU11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AV11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AW11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AX11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AY11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="AZ11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^3</f>
         <v/>
       </c>
       <c r="BA11" s="290">
@@ -21865,51 +21910,51 @@
         <v/>
       </c>
       <c r="BB11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BC11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BD11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BE11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BF11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BG11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BH11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BI11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BJ11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BK11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BL11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BM11" s="290">
-        <f>Assumptions!$D$66*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$66*(1+Assumptions!$E$66)^4</f>
         <v/>
       </c>
       <c r="BN11" s="290">
@@ -22542,51 +22587,51 @@
         </is>
       </c>
       <c r="B15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="C15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="D15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="E15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="F15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="G15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="H15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="I15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="J15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="K15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="L15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="M15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^0</f>
         <v/>
       </c>
       <c r="N15" s="290">
@@ -22594,51 +22639,51 @@
         <v/>
       </c>
       <c r="O15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="P15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="Q15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="R15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="S15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="T15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="U15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="V15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="W15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="X15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="Y15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="Z15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^1</f>
         <v/>
       </c>
       <c r="AA15" s="290">
@@ -22646,51 +22691,51 @@
         <v/>
       </c>
       <c r="AB15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AC15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AD15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AE15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AF15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AG15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AH15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AI15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AJ15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AK15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AL15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AM15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^2</f>
         <v/>
       </c>
       <c r="AN15" s="290">
@@ -22698,51 +22743,51 @@
         <v/>
       </c>
       <c r="AO15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AP15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AQ15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AR15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AS15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AT15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AU15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AV15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AW15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AX15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AY15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="AZ15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^3</f>
         <v/>
       </c>
       <c r="BA15" s="290">
@@ -22750,51 +22795,51 @@
         <v/>
       </c>
       <c r="BB15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BC15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BD15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BE15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BF15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BG15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BH15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BI15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BJ15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BK15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BL15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BM15" s="290">
-        <f>Assumptions!$D$67*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$67*(1+Assumptions!$E$67)^4</f>
         <v/>
       </c>
       <c r="BN15" s="290">
@@ -23427,51 +23472,51 @@
         </is>
       </c>
       <c r="B19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="C19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="D19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="E19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="F19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="G19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="H19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="I19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="J19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="K19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="L19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="M19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^0</f>
         <v/>
       </c>
       <c r="N19" s="290">
@@ -23479,51 +23524,51 @@
         <v/>
       </c>
       <c r="O19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="P19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="Q19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="R19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="S19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="T19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="U19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="V19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="W19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="X19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="Y19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="Z19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^1</f>
         <v/>
       </c>
       <c r="AA19" s="290">
@@ -23531,51 +23576,51 @@
         <v/>
       </c>
       <c r="AB19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AC19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AD19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AE19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AF19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AG19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AH19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AI19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AJ19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AK19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AL19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AM19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^2</f>
         <v/>
       </c>
       <c r="AN19" s="290">
@@ -23583,51 +23628,51 @@
         <v/>
       </c>
       <c r="AO19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AP19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AQ19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AR19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AS19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AT19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AU19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AV19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AW19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AX19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AY19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="AZ19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^3</f>
         <v/>
       </c>
       <c r="BA19" s="290">
@@ -23635,51 +23680,51 @@
         <v/>
       </c>
       <c r="BB19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BC19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BD19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BE19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BF19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BG19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BH19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BI19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BJ19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BK19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BL19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BM19" s="290">
-        <f>Assumptions!$D$68*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$68*(1+Assumptions!$E$68)^4</f>
         <v/>
       </c>
       <c r="BN19" s="290">
@@ -24312,51 +24357,51 @@
         </is>
       </c>
       <c r="B23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="C23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="D23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="E23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="F23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="G23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="H23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="I23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="J23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="K23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="L23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="M23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^0</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^0</f>
         <v/>
       </c>
       <c r="N23" s="290">
@@ -24364,51 +24409,51 @@
         <v/>
       </c>
       <c r="O23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="P23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="Q23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="R23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="S23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="T23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="U23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="V23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="W23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="X23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="Y23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="Z23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^1</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^1</f>
         <v/>
       </c>
       <c r="AA23" s="290">
@@ -24416,51 +24461,51 @@
         <v/>
       </c>
       <c r="AB23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AC23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AD23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AE23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AF23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AG23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AH23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AI23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AJ23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AK23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AL23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AM23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^2</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^2</f>
         <v/>
       </c>
       <c r="AN23" s="290">
@@ -24468,51 +24513,51 @@
         <v/>
       </c>
       <c r="AO23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AP23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AQ23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AR23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AS23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AT23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AU23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AV23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AW23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AX23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AY23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="AZ23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^3</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^3</f>
         <v/>
       </c>
       <c r="BA23" s="290">
@@ -24520,51 +24565,51 @@
         <v/>
       </c>
       <c r="BB23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BC23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BD23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BE23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BF23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BG23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BH23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BI23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BJ23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BK23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BL23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BM23" s="290">
-        <f>Assumptions!$D$69*(1+Assumptions!$C$24)^4</f>
+        <f>Assumptions!$D$69*(1+Assumptions!$E$69)^4</f>
         <v/>
       </c>
       <c r="BN23" s="290">
@@ -33417,51 +33462,51 @@
         </is>
       </c>
       <c r="B15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!B$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="C15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!C$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="D15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!D$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="E15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!E$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="F15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!F$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="G15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!G$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="H15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!H$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="I15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!I$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="J15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!J$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="K15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!K$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="L15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!L$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="M15" s="140">
-        <f>Form_V_MPBF!C11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!C11*Assumptions!$C$13/12*IF(Sales!$N$26=0,1,12*Sales!M$26/Sales!$N$26)</f>
         <v/>
       </c>
       <c r="N15" s="139">
@@ -33469,51 +33514,51 @@
         <v/>
       </c>
       <c r="O15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!O$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="P15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!P$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="Q15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!Q$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="R15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!R$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="S15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!S$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="T15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!T$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="U15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!U$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="V15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!V$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="W15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!W$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="X15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!X$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="Y15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!Y$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="Z15" s="140">
-        <f>Form_V_MPBF!D11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!D11*Assumptions!$C$13/12*IF(Sales!$AA$26=0,1,12*Sales!Z$26/Sales!$AA$26)</f>
         <v/>
       </c>
       <c r="AA15" s="139">
@@ -33521,51 +33566,51 @@
         <v/>
       </c>
       <c r="AB15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AB$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AC15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AC$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AD15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AD$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AE15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AE$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AF15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AF$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AG15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AG$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AH15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AH$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AI15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AI$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AJ15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AJ$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AK15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AK$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AL15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AL$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AM15" s="140">
-        <f>Form_V_MPBF!E11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!E11*Assumptions!$C$13/12*IF(Sales!$AN$26=0,1,12*Sales!AM$26/Sales!$AN$26)</f>
         <v/>
       </c>
       <c r="AN15" s="139">
@@ -33573,51 +33618,51 @@
         <v/>
       </c>
       <c r="AO15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AO$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AP15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AP$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AQ15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AQ$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AR15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AR$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AS15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AS$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AT15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AT$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AU15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AU$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AV15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AV$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AW15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AW$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AX15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AX$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AY15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AY$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="AZ15" s="140">
-        <f>Form_V_MPBF!F11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!F11*Assumptions!$C$13/12*IF(Sales!$BA$26=0,1,12*Sales!AZ$26/Sales!$BA$26)</f>
         <v/>
       </c>
       <c r="BA15" s="139">
@@ -33625,51 +33670,51 @@
         <v/>
       </c>
       <c r="BB15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BB$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BC15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BC$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BD15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BD$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BE15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BE$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BF15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BF$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BG15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BG$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BH15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BH$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BI15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BI$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BJ15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BJ$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BK15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BK$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BL15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BL$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BM15" s="140">
-        <f>Form_V_MPBF!G11*Assumptions!$C$13/12</f>
+        <f>Form_V_MPBF!G11*Assumptions!$C$13/12*IF(Sales!$BN$26=0,1,12*Sales!BM$26/Sales!$BN$26)</f>
         <v/>
       </c>
       <c r="BN15" s="139">

--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -4863,23 +4863,23 @@
         </is>
       </c>
       <c r="C10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!C14*(1-Assumptions!$C$55)-Form_IV_CA_CL!C18)</f>
+        <f>MAX(0,Form_IV_CA_CL!C14*0.75-Form_IV_CA_CL!C18)</f>
         <v/>
       </c>
       <c r="D10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!D14*(1-Assumptions!$C$55)-Form_IV_CA_CL!D18)</f>
+        <f>MAX(0,Form_IV_CA_CL!D14*0.75-Form_IV_CA_CL!D18)</f>
         <v/>
       </c>
       <c r="E10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!E14*(1-Assumptions!$C$55)-Form_IV_CA_CL!E18)</f>
+        <f>MAX(0,Form_IV_CA_CL!E14*0.75-Form_IV_CA_CL!E18)</f>
         <v/>
       </c>
       <c r="F10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!F14*(1-Assumptions!$C$55)-Form_IV_CA_CL!F18)</f>
+        <f>MAX(0,Form_IV_CA_CL!F14*0.75-Form_IV_CA_CL!F18)</f>
         <v/>
       </c>
       <c r="G10" s="143">
-        <f>MAX(0,Form_IV_CA_CL!G14*(1-Assumptions!$C$55)-Form_IV_CA_CL!G18)</f>
+        <f>MAX(0,Form_IV_CA_CL!G14*0.75-Form_IV_CA_CL!G18)</f>
         <v/>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
           <t>M12</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="81" t="inlineStr">
         <is>
           <t>Gestation (months, 0-11)</t>
         </is>
@@ -10946,7 +10946,7 @@
       <c r="L21" s="126" t="n"/>
       <c r="M21" s="126" t="n"/>
       <c r="N21" s="126" t="n"/>
-      <c r="O21" t="n">
+      <c r="O21" s="81" t="n">
         <v>0</v>
       </c>
       <c r="S21" s="81" t="inlineStr">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="D32" s="335" t="n"/>
       <c r="E32" s="336" t="n"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="81" t="inlineStr">
         <is>
           <t>(headcount)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="81" t="inlineStr">
         <is>
           <t>(₹ / employee / month)</t>
         </is>

--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -4666,7 +4666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="81" min="1" max="1"/>
@@ -4886,27 +4886,81 @@
     <row r="11" ht="15" customHeight="1" s="82">
       <c r="B11" s="137" t="inlineStr">
         <is>
-          <t>Recommended MPBF  (Method II)</t>
+          <t>Recommended MPBF (Method II, net of surplus cash)</t>
         </is>
       </c>
       <c r="C11" s="139">
-        <f>C10</f>
+        <f>MAX(0,C10-C13)</f>
         <v/>
       </c>
       <c r="D11" s="139">
-        <f>D10</f>
+        <f>MAX(0,D10-D13)</f>
         <v/>
       </c>
       <c r="E11" s="139">
-        <f>E10</f>
+        <f>MAX(0,E10-E13)</f>
         <v/>
       </c>
       <c r="F11" s="139">
-        <f>F10</f>
+        <f>MAX(0,F10-F13)</f>
         <v/>
       </c>
       <c r="G11" s="139">
-        <f>G10</f>
+        <f>MAX(0,G10-G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cumulative free cash generated (before WC draw)</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>Annual_Summary!C27-(Assumptions!$C$42+Assumptions!$C$43+Assumptions!$C$45+Assumptions!$C$47)-(Repayment!C7+'Existing Loan'!C15)</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>C12+Annual_Summary!D27-(Repayment!D7+'Existing Loan'!D15)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>D12+Annual_Summary!E27-(Repayment!E7+'Existing Loan'!E15)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>E12+Annual_Summary!F27-(Repayment!F7+'Existing Loan'!F15)</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>F12+Annual_Summary!G27-(Repayment!G7+'Existing Loan'!G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Available surplus over minimum cash buffer</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>MAX(0,C12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>MAX(0,D12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>MAX(0,E12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>MAX(0,F12-Assumptions!$C$54)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>MAX(0,G12-Assumptions!$C$54)</f>
         <v/>
       </c>
     </row>
@@ -9403,7 +9457,18 @@
         <v/>
       </c>
       <c r="D25" s="171">
-        <f>IF(AVERAGE(DSCR!C14:G14)&gt;=1.5,"STRONG — comfortably serviceable (avg DSCR &gt;= 1.50)",IF(AVERAGE(DSCR!C14:G14)&gt;=1.2,"BANKABLE — meets the 1.20 minimum DSCR","BELOW NORM — average DSCR under the 1.20 bank floor"))</f>
+        <f>IFERROR(IF(OR(MAX(Annual_Summary!C22/Annual_Summary!C8,Annual_Summary!D22/Annual_Summary!D8,Annual_Summary!E22/Annual_Summary!E8,Annual_Summary!F22/Annual_Summary!F8,Annual_Summary!G22/Annual_Summary!G8)&gt;0.4,Annual_Summary!C8/(C10+C11)&lt;0.3,Annual_Summary!C8/(C10+C11)&gt;8,AVERAGE(DSCR!C14:G14)&gt;10),"REVIEW REQUIRED — figures need verification (EBITDA margin, revenue/cost scale, or DSCR outside normal range)",IF(AND(AVERAGE(DSCR!C14:G14)&gt;=1.5,MIN(DSCR!C14:G14)&gt;=1.25),"STRONG — comfortably serviceable (avg DSCR &gt;= 1.50, minimum-year DSCR &gt;= 1.25)",IF(AND(AVERAGE(DSCR!C14:G14)&gt;=1.2,MIN(DSCR!C14:G14)&gt;=1.0),"BANKABLE — meets the 1.20 minimum average DSCR with no year below 1.00","BELOW NORM — average or minimum-year DSCR under the bank floor"))),"REVIEW REQUIRED — could not verify DSCR / scale ratios (check inputs)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="81" t="inlineStr">
+        <is>
+          <t>Minimum DSCR (5-yr)</t>
+        </is>
+      </c>
+      <c r="C26" s="81">
+        <f>MIN(DSCR!C14:G14)</f>
         <v/>
       </c>
     </row>
@@ -9819,7 +9884,7 @@
       </c>
       <c r="T8" s="81" t="inlineStr">
         <is>
-          <t>Installed Capacity</t>
+          <t>Installed Capacity (state your own unit -- tonnes/kg/pieces/sq.ft p.a. -- matching what you specified)</t>
         </is>
       </c>
       <c r="U8" s="81" t="inlineStr">

--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -4911,56 +4911,55 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Cumulative free cash generated (before WC draw)</t>
         </is>
       </c>
-      <c r="C12">
+      <c r="C12" s="81">
         <f>Annual_Summary!C27-(Assumptions!$C$42+Assumptions!$C$43+Assumptions!$C$45+Assumptions!$C$47)-(Repayment!C7+'Existing Loan'!C15)</f>
         <v/>
       </c>
-      <c r="D12">
+      <c r="D12" s="81">
         <f>C12+Annual_Summary!D27-(Repayment!D7+'Existing Loan'!D15)</f>
         <v/>
       </c>
-      <c r="E12">
+      <c r="E12" s="81">
         <f>D12+Annual_Summary!E27-(Repayment!E7+'Existing Loan'!E15)</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="81">
         <f>E12+Annual_Summary!F27-(Repayment!F7+'Existing Loan'!F15)</f>
         <v/>
       </c>
-      <c r="G12">
+      <c r="G12" s="81">
         <f>F12+Annual_Summary!G27-(Repayment!G7+'Existing Loan'!G15)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Available surplus over minimum cash buffer</t>
-        </is>
-      </c>
-      <c r="C13">
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>Available surplus carried in from prior years (over min. cash buffer)</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="81">
         <f>MAX(0,C12-Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="D13">
+      <c r="E13" s="81">
         <f>MAX(0,D12-Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="E13">
+      <c r="F13" s="81">
         <f>MAX(0,E12-Assumptions!$C$54)</f>
         <v/>
       </c>
-      <c r="F13">
+      <c r="G13" s="81">
         <f>MAX(0,F12-Assumptions!$C$54)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>MAX(0,G12-Assumptions!$C$54)</f>
         <v/>
       </c>
     </row>

--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -3560,10 +3560,14 @@
     <row r="28" ht="15" customHeight="1" s="82">
       <c r="B28" s="88" t="inlineStr">
         <is>
-          <t>DSCR — Debt-service coverage year by year</t>
-        </is>
-      </c>
-      <c r="C28" s="132" t="n"/>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Debt-service coverage year by year</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="90" t="inlineStr">
@@ -3606,11 +3610,10 @@
       <c r="C32" s="88" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B13" location="Assumptions!A1" display="Assumptions"/>

--- a/templates/bank_loan/CMA_Dashboard_Premium.xlsx
+++ b/templates/bank_loan/CMA_Dashboard_Premium.xlsx
@@ -3563,7 +3563,7 @@
           <t>DSCR</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="81" t="inlineStr">
         <is>
           <t>Debt-service coverage year by year</t>
         </is>
@@ -3611,9 +3611,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B13" location="Assumptions!A1" display="Assumptions"/>
@@ -9526,7 +9526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF75"/>
+  <dimension ref="A1:AF87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="81" min="1" max="1"/>
@@ -11724,6 +11724,142 @@
         <is>
           <t>months</t>
         </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>K.  COST OF PROJECT  (bottom-up build-up; ties to Means of Finance below)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Fixed assets (land + building + plant &amp; machinery + furniture)</t>
+        </is>
+      </c>
+      <c r="C78">
+        <f>C42+C43+C45+C47</f>
+        <v/>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pre-operative &amp; preliminary expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Margin money for working capital  (borrower's stipulated NWC, Year 1)</t>
+        </is>
+      </c>
+      <c r="C80">
+        <f>'WC &amp; CC-OD Limit'!C10</f>
+        <v/>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TOTAL PROJECT COST</t>
+        </is>
+      </c>
+      <c r="C81">
+        <f>C78+C79+C80</f>
+        <v/>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MEANS OF FINANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Term loan</t>
+        </is>
+      </c>
+      <c r="C84">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Promoter's contribution</t>
+        </is>
+      </c>
+      <c r="C85">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TOTAL MEANS OF FINANCE</t>
+        </is>
+      </c>
+      <c r="C86">
+        <f>C84+C85</f>
+        <v/>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>₹</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Check  (Total Project Cost − Total Means of Finance = 0)</t>
+        </is>
+      </c>
+      <c r="C87">
+        <f>C81-C86</f>
+        <v/>
       </c>
     </row>
   </sheetData>
